--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.4389027523285</v>
+        <v>3.97132169725338</v>
       </c>
       <c r="D2" t="n">
-        <v>23.75851948961913</v>
+        <v>3.860759417063108</v>
       </c>
       <c r="E2" t="n">
-        <v>5.103959887044526</v>
+        <v>0.8293934816447353</v>
       </c>
       <c r="F2" t="n">
-        <v>4.685652221467407</v>
+        <v>0.7614184859884536</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.23098297823944</v>
+        <v>2.31253473396391</v>
       </c>
       <c r="D3" t="n">
-        <v>14.38721504668431</v>
+        <v>2.337922445086201</v>
       </c>
       <c r="E3" t="n">
-        <v>5.103959887044526</v>
+        <v>0.8293934816447353</v>
       </c>
       <c r="F3" t="n">
-        <v>4.685652221467407</v>
+        <v>0.7614184859884536</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
